--- a/results/log_pv_cap_fit/log_pv_cap_fit_densities_hdensity_estimates.xlsx
+++ b/results/log_pv_cap_fit/log_pv_cap_fit_densities_hdensity_estimates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,41 +462,11 @@
           <t>densities-ML_ErrorFE-queen-Running ML_ErrorFE:queen for log_pv_cap_fit ~ (densities): hdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-inverse_distance-Running PooledOLS:inverse_distance for log_pv_cap_fit ~ (densities): hdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-k_nearest-Running PooledOLS:k_nearest for log_pv_cap_fit ~ (densities): hdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-queen-Running PooledOLS:queen for log_pv_cap_fit ~ (densities): hdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-inverse_distance-Running PanelRE:inverse_distance for log_pv_cap_fit ~ (densities): hdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-k_nearest-Running PanelRE:k_nearest for log_pv_cap_fit ~ (densities): hdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-queen-Running PanelRE:queen for log_pv_cap_fit ~ (densities): hdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hdensity</t>
+          <t>D(Households)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,43 +512,13 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>0.003***</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>-0.017***</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-0.017***</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>-0.017***</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>-0.007***</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>-0.007***</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>-0.007***</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -624,43 +564,13 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>0.307***</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>-0.724***</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-0.724***</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-0.724***</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2.170***</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2.170***</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2.170***</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -706,43 +616,13 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>0.001</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.039***</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.039***</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.039***</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.003</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.003</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0.003</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -788,126 +668,96 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>0.152***</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.535***</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0.535***</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0.535***</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-0.240***</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>-0.240***</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-0.240***</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W_hdensity</t>
+          <t>Spatial term, ρ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.006</t>
+          <t>0.899***</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.008***</t>
+          <t>0.738***</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.006***</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>0.616***</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.961***</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.812***</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.710***</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W_log_income</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.389**</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.629***</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.853***</t>
-        </is>
-      </c>
+          <t>Spatial term, λ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.977***</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.910***</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.854***</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W_log_hholds</t>
+          <t>W(D(Households))</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.049*</t>
+          <t>-0.006</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.003</t>
+          <t>-0.008***</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.005*</t>
+          <t>-0.006***</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -916,32 +766,26 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W_log_sunny_hours</t>
+          <t>W(Income)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-0.225***</t>
+          <t>0.389**</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.290***</t>
+          <t>0.629***</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.316***</t>
+          <t>0.853***</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -950,891 +794,320 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W_log_pv_cap_fit</t>
+          <t>W(Households)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.899***</t>
+          <t>-0.049*</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.738***</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.616***</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.961***</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.812***</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.710***</t>
-        </is>
-      </c>
+          <t>-0.005*</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>r2</t>
+          <t>W(Sunny hours)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.881</t>
+          <t>-0.225***</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.863</t>
+          <t>-0.290***</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.845</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.880</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.861</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.839</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.180</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.403</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.466</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.259</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.259</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.259</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.031</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.031</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.031</t>
-        </is>
-      </c>
+          <t>-0.316***</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>aic</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-10004.929</t>
+          <t>0.881</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-9564.104</t>
+          <t>0.863</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-9288.367</t>
+          <t>0.845</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-9984.569</t>
+          <t>0.880</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-9477.955</t>
+          <t>0.861</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-9132.626</t>
+          <t>0.839</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-9989.892</t>
+          <t>0.180</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-9378.502</t>
+          <t>0.403</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-8928.280</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1128.738</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1128.738</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>1128.738</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2617.242</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2617.242</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2617.242</t>
+          <t>0.466</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>schwarz</t>
+          <t>AIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-9954.185</t>
+          <t>-10004.929</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-9513.361</t>
+          <t>-9564.104</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-9237.623</t>
+          <t>-9288.367</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-9956.378</t>
+          <t>-9984.569</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-9449.764</t>
+          <t>-9477.955</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-9104.435</t>
+          <t>-9132.626</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-9967.339</t>
+          <t>-9989.892</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-9355.949</t>
+          <t>-9378.502</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-8905.727</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>1156.929</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>1156.929</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>1156.929</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2645.433</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2645.433</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2645.433</t>
+          <t>-8928.280</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>llr</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5011.464</t>
+          <t>-9954.185</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4791.052</t>
+          <t>-9513.361</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4653.183</t>
+          <t>-9237.623</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4997.284</t>
+          <t>-9956.378</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4743.977</t>
+          <t>-9449.764</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4571.313</t>
+          <t>-9104.435</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4998.946</t>
+          <t>-9967.339</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4693.251</t>
+          <t>-9355.949</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4468.140</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>-559.369</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-559.369</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>-559.369</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-1303.621</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>-1303.621</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>-1303.621</t>
+          <t>-8905.727</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>n_obs</t>
+          <t>Log-Likelihood</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>5011.464</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4791.052</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4653.183</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4997.284</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4743.977</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4571.313</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4998.946</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4693.251</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2076</t>
+          <t>4468.140</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tests</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df  p-value
-0       LM Marginal RE (LM1)    66.860170   1      0.0
-1  LM Marginal Spatial (LM2)    19.085711   1      0.0
-2             LM Joint (LMJ)  4834.546687   2      0.0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df  p-value
-0       LM Marginal RE (LM1)    66.860170   1      0.0
-1  LM Marginal Spatial (LM2)     8.590409   1      0.0
-2             LM Joint (LMJ)  4544.077465   2      0.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df       p-value
-0       LM Marginal RE (LM1)    66.860170   1  0.000000e+00
-1  LM Marginal Spatial (LM2)     8.065190   1  3.330669e-16
-2             LM Joint (LMJ)  4535.329614   2  0.000000e+00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test   Statistic df p-value
-0      LM Conditional Spatial   161.47462  1     0.0
-1  Hausman Specification Test  204.377423  4     0.0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test   Statistic df p-value
-0      LM Conditional Spatial   39.846193  1     0.0
-1  Hausman Specification Test  204.377423  4     0.0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test   Statistic df p-value
-0      LM Conditional Spatial   26.828011  1     0.0
-1  Hausman Specification Test  204.377423  4     0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>outputs</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           hdensity     0.002999  0.000624   4.805109  0.000002
-1         log_income     0.052102  0.069866   0.745742  0.455823
-2         log_hholds    -0.000512  0.001157  -0.443017  0.657753
-3    log_sunny_hours      0.11077  0.032785   3.378681  0.000728
-4         W_hdensity     -0.00629  0.006888  -0.913167  0.361155
-5       W_log_income     0.388994  0.130517    2.98041  0.002879
-6       W_log_hholds    -0.049326  0.020707   -2.38205  0.017217
-7  W_log_sunny_hours     -0.22488  0.052387  -4.292661  0.000018
-8   W_log_pv_cap_fit     0.898716  0.025638  35.053908       0.0</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           hdensity     0.002139  0.000665   3.215884    0.0013
-1         log_income     0.105757  0.071593   1.477192  0.139624
-2         log_hholds    -0.000036   0.00124  -0.029386  0.976557
-3    log_sunny_hours     0.099643  0.033359    2.98697  0.002818
-4         W_hdensity    -0.008224  0.001814  -4.534212  0.000006
-5       W_log_income     0.628923  0.090009    6.98733       0.0
-6       W_log_hholds    -0.003034  0.003703  -0.819223  0.412659
-7  W_log_sunny_hours    -0.289659  0.044245   -6.54674       0.0
-8   W_log_pv_cap_fit      0.73795  0.019179  38.476346       0.0</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           hdensity     0.001825  0.000708   2.578304  0.009929
-1         log_income     0.158085  0.072922   2.167858  0.030169
-2         log_hholds    -0.000152  0.001319  -0.114919   0.90851
-3    log_sunny_hours     0.077169  0.034686   2.224797  0.026095
-4         W_hdensity    -0.006035  0.001193  -5.057278       0.0
-5       W_log_income     0.852971  0.085455   9.981567       0.0
-6       W_log_hholds    -0.004787  0.002211  -2.165363   0.03036
-7  W_log_sunny_hours    -0.316187  0.043454   -7.27642       0.0
-8   W_log_pv_cap_fit     0.616418  0.020632  29.876256       0.0</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          var_names coefficients   std_err    zt_stat      prob
-0          hdensity      0.00276   0.00062   4.452108  0.000009
-1        log_income     0.061124  0.029087   2.101432  0.035603
-2        log_hholds    -0.000334  0.001158  -0.288634  0.772861
-3   log_sunny_hours     0.036533  0.022876   1.597029  0.110259
-4  W_log_pv_cap_fit      0.96096  0.010146  94.714881       0.0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          var_names coefficients   std_err    zt_stat      prob
-0          hdensity     0.002227  0.000669   3.327338  0.000877
-1        log_income     0.406978  0.036805  11.057569       0.0
-2        log_hholds     0.000431   0.00125   0.344845  0.730211
-3   log_sunny_hours    -0.006174  0.023984   -0.25743  0.796847
-4  W_log_pv_cap_fit     0.812315  0.014108  57.577306       0.0</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          var_names coefficients   std_err    zt_stat      prob
-0          hdensity      0.00214   0.00072   2.970931  0.002969
-1        log_income     0.627553  0.041822  15.005389       0.0
-2        log_hholds     0.000421  0.001345   0.312795  0.754436
-3   log_sunny_hours    -0.026999  0.025792  -1.046786  0.295198
-4  W_log_pv_cap_fit     0.709696  0.016322  43.479904       0.0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err     zt_stat      prob
-0         hdensity     0.003003  0.000625    4.807598  0.000002
-1       log_income     0.066982  0.069701    0.960993  0.336556
-2       log_hholds    -0.000179  0.001151   -0.155366  0.876533
-3  log_sunny_hours     0.111066  0.032823    3.383803  0.000715
-4           lambda     0.977122  0.006384  153.066743       0.0</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err     zt_stat      prob
-0         hdensity     0.003017  0.000646     4.67327  0.000003
-1       log_income     0.206586  0.069462    2.974096  0.002939
-2       log_hholds     0.000615   0.00118    0.520983  0.602379
-3  log_sunny_hours     0.135994  0.033514    4.057854   0.00005
-4           lambda     0.909724  0.008639  105.306754       0.0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         hdensity     0.003373  0.000662   5.091249       0.0
-1       log_income     0.307091    0.0705   4.355934  0.000013
-2       log_hholds     0.000897  0.001198   0.748363  0.454242
-3  log_sunny_hours     0.151551    0.0354   4.281137  0.000019
-4           lambda     0.853559  0.011662  73.191693       0.0</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     5.001486  0.499677  10.009438       0.0
-1         hdensity    -0.016976  0.000802 -21.165803       0.0
-2       log_income    -0.724046  0.074881  -9.669232       0.0
-3       log_hholds     0.038872  0.008591   4.524709  0.000006
-4  log_sunny_hours     0.534863   0.15224     3.5133  0.000452</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     5.001486  0.499677  10.009438       0.0
-1         hdensity    -0.016976  0.000802 -21.165803       0.0
-2       log_income    -0.724046  0.074881  -9.669232       0.0
-3       log_hholds     0.038872  0.008591   4.524709  0.000006
-4  log_sunny_hours     0.534863   0.15224     3.5133  0.000452</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     5.001486  0.499677  10.009438       0.0
-1         hdensity    -0.016976  0.000802 -21.165803       0.0
-2       log_income    -0.724046  0.074881  -9.669232       0.0
-3       log_hholds     0.038872  0.008591   4.524709  0.000006
-4  log_sunny_hours     0.534863   0.15224     3.5133  0.000452</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.815587  0.211809 -22.735503       0.0
-1         hdensity    -0.007282  0.001071  -6.797449       0.0
-2       log_income     2.169869  0.044556   48.70033       0.0
-3       log_hholds     0.002937  0.002342   1.254173  0.209779
-4  log_sunny_hours     -0.23989  0.045079  -5.321506       0.0</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.815587  0.211809 -22.735503       0.0
-1         hdensity    -0.007282  0.001071  -6.797449       0.0
-2       log_income     2.169869  0.044556   48.70033       0.0
-3       log_hholds     0.002937  0.002342   1.254173  0.209779
-4  log_sunny_hours     -0.23989  0.045079  -5.321506       0.0</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.815587  0.211809 -22.735503       0.0
-1         hdensity    -0.007282  0.001071  -6.797449       0.0
-2       log_income     2.169869  0.044556   48.70033       0.0
-3       log_hholds     0.002937  0.002342   1.254173  0.209779
-4  log_sunny_hours     -0.23989  0.045079  -5.321506       0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>effects</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_inverse_distance  \
-hdensity                                    -0.032492   
-log_income                                   4.355040   
-log_hholds                                  -0.492068   
-log_sunny_hours                             -1.126640   
-                 direct_ML_LagFE(SLX)_inverse_distance  \
-hdensity                                      0.002999   
-log_income                                    0.052102   
-log_hholds                                   -0.000512   
-log_sunny_hours                               0.110770   
-                 indirect_ML_LagFE(SLX)_inverse_distance  
-hdensity                                       -0.035491  
-log_income                                      4.302938  
-log_hholds                                     -0.491555  
-log_sunny_hours                                -1.237409  </t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_k_nearest  \
-hdensity                             -0.023220   
-log_income                            2.803587   
-log_hholds                           -0.011715   
-log_sunny_hours                      -0.725112   
-                 direct_ML_LagFE(SLX)_k_nearest  \
-hdensity                               0.002139   
-log_income                             0.105757   
-log_hholds                            -0.000036   
-log_sunny_hours                        0.099643   
-                 indirect_ML_LagFE(SLX)_k_nearest  
-hdensity                                -0.025359  
-log_income                               2.697830  
-log_hholds                              -0.011679  
-log_sunny_hours                         -0.824756  </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_queen  direct_ML_LagFE(SLX)_queen  \
-hdensity                         -0.010977                    0.001825   
-log_income                        2.635825                    0.158085   
-log_hholds                       -0.012876                   -0.000152   
-log_sunny_hours                  -0.623119                    0.077169   
-                 indirect_ML_LagFE(SLX)_queen  
-hdensity                            -0.012802  
-log_income                           2.477740  
-log_hholds                          -0.012725  
-log_sunny_hours                     -0.700288  </t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_inverse_distance  \
-hdensity                                0.070694   
-log_income                              1.565680   
-log_hholds                             -0.008558   
-log_sunny_hours                         0.935790   
-                 direct_ML_LagFE_inverse_distance  \
-hdensity                                 0.002760   
-log_income                               0.061124   
-log_hholds                              -0.000334   
-log_sunny_hours                          0.036533   
-                 indirect_ML_LagFE_inverse_distance  
-hdensity                                   0.067934  
-log_income                                 1.504557  
-log_hholds                                -0.008224  
-log_sunny_hours                            0.899257  </t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_k_nearest  direct_ML_LagFE_k_nearest  \
-hdensity                         0.011867                   0.002227   
-log_income                       2.168411                   0.406978   
-log_hholds                       0.002297                   0.000431   
-log_sunny_hours                 -0.032896                  -0.006174   
-                 indirect_ML_LagFE_k_nearest  
-hdensity                            0.009639  
-log_income                          1.761433  
-log_hholds                          0.001866  
-log_sunny_hours                    -0.026722  </t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_queen  direct_ML_LagFE_queen  \
-hdensity                     0.007373               0.002140   
-log_income                   2.161710               0.627553   
-log_hholds                   0.001450               0.000421   
-log_sunny_hours             -0.093002              -0.026999   
-                 indirect_ML_LagFE_queen  
-hdensity                        0.005232  
-log_income                      1.534157  
-log_hholds                      0.001029  
-log_sunny_hours                -0.066003  </t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>lambda</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0.977***</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0.910***</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0.854***</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CONSTANT</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>5.001***</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>5.001***</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>5.001***</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-4.816***</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>-4.816***</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>-4.816***</t>
+          <t>N obs.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2076</t>
         </is>
       </c>
     </row>
